--- a/00_code_base/02_unidirectional/output_capacity_use_PLANNED.xlsx
+++ b/00_code_base/02_unidirectional/output_capacity_use_PLANNED.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\00_code_base\02_unidirectional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{130C0406-1EF0-4B6C-A85C-BF603DCB340E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3472DA4-64C2-4AB4-9575-3E6E1765B2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="242">
   <si>
     <t>Commodity</t>
   </si>
@@ -754,6 +754,12 @@
   </si>
   <si>
     <t>Share_Used</t>
+  </si>
+  <si>
+    <t>('EE', 'LV')</t>
+  </si>
+  <si>
+    <t>('LV', 'EE')</t>
   </si>
 </sst>
 </file>
@@ -823,7 +829,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1129,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1163,7 +1169,7 @@
         <v>111.378</v>
       </c>
       <c r="E2">
-        <f>VLOOKUP(C2,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C2,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>111.378</v>
       </c>
       <c r="F2" s="3">
@@ -1185,7 +1191,7 @@
         <v>322.41000000000003</v>
       </c>
       <c r="E3">
-        <f>VLOOKUP(C3,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C3,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>322.40999999999997</v>
       </c>
       <c r="F3" s="3">
@@ -1207,7 +1213,7 @@
         <v>73.274999999999991</v>
       </c>
       <c r="E4">
-        <f>VLOOKUP(C4,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C4,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>73.274999999999991</v>
       </c>
       <c r="F4" s="3">
@@ -1229,7 +1235,7 @@
         <v>155.83150000000001</v>
       </c>
       <c r="E5">
-        <f>VLOOKUP(C5,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C5,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>155.83149999999998</v>
       </c>
       <c r="F5" s="3">
@@ -1251,7 +1257,7 @@
         <v>25.402000000000001</v>
       </c>
       <c r="E6">
-        <f>VLOOKUP(C6,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C6,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>25.402000000000001</v>
       </c>
       <c r="F6" s="3">
@@ -1270,15 +1276,15 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>36.225957569754172</v>
+        <v>39.08</v>
       </c>
       <c r="E7">
-        <f>VLOOKUP(C7,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C7,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>39.08</v>
       </c>
       <c r="F7" s="3">
         <f t="shared" si="0"/>
-        <v>0.92696923156996347</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1295,7 +1301,7 @@
         <v>122.125</v>
       </c>
       <c r="E8">
-        <f>VLOOKUP(C8,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C8,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>122.125</v>
       </c>
       <c r="F8" s="3">
@@ -1317,7 +1323,7 @@
         <v>60.573999999999998</v>
       </c>
       <c r="E9">
-        <f>VLOOKUP(C9,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C9,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>60.573999999999998</v>
       </c>
       <c r="F9" s="3">
@@ -1339,7 +1345,7 @@
         <v>58.62</v>
       </c>
       <c r="E10">
-        <f>VLOOKUP(C10,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C10,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>74.251999999999995</v>
       </c>
       <c r="F10" s="3">
@@ -1361,7 +1367,7 @@
         <v>398.45400000000001</v>
       </c>
       <c r="E11">
-        <f>VLOOKUP(C11,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C11,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>655.56699999999989</v>
       </c>
       <c r="F11" s="3">
@@ -1383,7 +1389,7 @@
         <v>425.97199999999998</v>
       </c>
       <c r="E12">
-        <f>VLOOKUP(C12,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C12,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>425.97199999999998</v>
       </c>
       <c r="F12" s="3">
@@ -1402,15 +1408,15 @@
         <v>15</v>
       </c>
       <c r="D13">
-        <v>416.41153114000019</v>
+        <v>425.48233619331592</v>
       </c>
       <c r="E13">
-        <f>VLOOKUP(C13,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C13,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>510.97099999999995</v>
       </c>
       <c r="F13" s="3">
         <f t="shared" si="0"/>
-        <v>0.81494161339880389</v>
+        <v>0.83269370706618573</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1424,15 +1430,15 @@
         <v>16</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>6.6570737613344084</v>
       </c>
       <c r="E14">
-        <f>VLOOKUP(C14,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C14,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>24.424999999999997</v>
       </c>
       <c r="F14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27255163813037497</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1449,7 +1455,7 @@
         <v>19.54</v>
       </c>
       <c r="E15">
-        <f>VLOOKUP(C15,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C15,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>48.849999999999994</v>
       </c>
       <c r="F15" s="3">
@@ -1471,7 +1477,7 @@
         <v>304.82400000000001</v>
       </c>
       <c r="E16">
-        <f>VLOOKUP(C16,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C16,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>304.82399999999996</v>
       </c>
       <c r="F16" s="3">
@@ -1493,7 +1499,7 @@
         <v>24.864095362311311</v>
       </c>
       <c r="E17">
-        <f>VLOOKUP(C17,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C17,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>25.402000000000001</v>
       </c>
       <c r="F17" s="3">
@@ -1512,15 +1518,15 @@
         <v>20</v>
       </c>
       <c r="D18">
+        <v>11.8009575697542</v>
+      </c>
+      <c r="E18">
+        <f>VLOOKUP(C18,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>14.654999999999999</v>
       </c>
-      <c r="E18">
-        <f>VLOOKUP(C18,Sheet2!$C$1:$D$147,2,FALSE)</f>
-        <v>14.654999999999999</v>
-      </c>
       <c r="F18" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.8052512841865711</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1537,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <f>VLOOKUP(C19,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C19,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F19" s="3">
@@ -1559,7 +1565,7 @@
         <v>13.947075570000001</v>
       </c>
       <c r="E20">
-        <f>VLOOKUP(C20,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C20,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F20" s="3">
@@ -1581,7 +1587,7 @@
         <v>47.618979999999993</v>
       </c>
       <c r="E21">
-        <f>VLOOKUP(C21,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C21,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F21" s="3">
@@ -1603,7 +1609,7 @@
         <v>38.415640000000003</v>
       </c>
       <c r="E22">
-        <f>VLOOKUP(C22,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C22,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F22" s="3">
@@ -1625,7 +1631,7 @@
         <v>129.941</v>
       </c>
       <c r="E23">
-        <f>VLOOKUP(C23,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C23,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F23" s="3">
@@ -1647,7 +1653,7 @@
         <v>234.14902171</v>
       </c>
       <c r="E24">
-        <f>VLOOKUP(C24,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C24,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F24" s="3">
@@ -1669,7 +1675,7 @@
         <v>1135.33376309</v>
       </c>
       <c r="E25">
-        <f>VLOOKUP(C25,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C25,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F25" s="3">
@@ -1691,7 +1697,7 @@
         <v>54.642437600000001</v>
       </c>
       <c r="E26">
-        <f>VLOOKUP(C26,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C26,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F26" s="3">
@@ -1713,7 +1719,7 @@
         <v>88.09608999999999</v>
       </c>
       <c r="E27">
-        <f>VLOOKUP(C27,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C27,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F27" s="3">
@@ -1735,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <f>VLOOKUP(C28,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C28,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F28" s="3">
@@ -1757,7 +1763,7 @@
         <v>18.562999999999999</v>
       </c>
       <c r="E29">
-        <f>VLOOKUP(C29,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C29,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F29" s="3">
@@ -1779,7 +1785,7 @@
         <v>320.81311304000002</v>
       </c>
       <c r="E30">
-        <f>VLOOKUP(C30,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C30,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F30" s="3">
@@ -1801,7 +1807,7 @@
         <v>190.67132000000001</v>
       </c>
       <c r="E31">
-        <f>VLOOKUP(C31,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C31,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F31" s="3">
@@ -1820,15 +1826,15 @@
         <v>34</v>
       </c>
       <c r="D32">
-        <v>28.89964418000022</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <f>VLOOKUP(C32,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C32,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>237.87050000000002</v>
       </c>
       <c r="F32" s="3">
         <f t="shared" si="0"/>
-        <v>0.12149318297140763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -1845,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <f>VLOOKUP(C33,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C33,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>140.52500000000001</v>
       </c>
       <c r="F33" s="3">
@@ -1867,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <f>VLOOKUP(C34,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C34,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>293.24099999999999</v>
       </c>
       <c r="F34" s="3">
@@ -1889,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <f>VLOOKUP(C35,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C35,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>120.88800000000001</v>
       </c>
       <c r="F35" s="3">
@@ -1908,15 +1914,15 @@
         <v>38</v>
       </c>
       <c r="D36">
+        <v>88.911405819999771</v>
+      </c>
+      <c r="E36">
+        <f>VLOOKUP(C36,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>117.81104999999999</v>
       </c>
-      <c r="E36">
-        <f>VLOOKUP(C36,Sheet2!$C$1:$D$147,2,FALSE)</f>
-        <v>117.81104999999999</v>
-      </c>
       <c r="F36" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0.7546949612960735</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -1933,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <f>VLOOKUP(C37,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C37,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>317.55</v>
       </c>
       <c r="F37" s="3">
@@ -1955,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <f>VLOOKUP(C38,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C38,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>509.97800000000001</v>
       </c>
       <c r="F38" s="3">
@@ -1974,15 +1980,15 @@
         <v>41</v>
       </c>
       <c r="D39">
-        <v>350.40602171</v>
+        <v>388.37647094331601</v>
       </c>
       <c r="E39">
-        <f>VLOOKUP(C39,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C39,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>702.90714500000001</v>
       </c>
       <c r="F39" s="3">
         <f t="shared" si="0"/>
-        <v>0.49850968823200681</v>
+        <v>0.55252884211799558</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -1999,7 +2005,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <f>VLOOKUP(C40,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C40,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>144.59475</v>
       </c>
       <c r="F40" s="3">
@@ -2021,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <f>VLOOKUP(C41,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C41,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>594.33059500000013</v>
       </c>
       <c r="F41" s="3">
@@ -2040,15 +2046,15 @@
         <v>44</v>
       </c>
       <c r="D42">
-        <v>116.57971494668421</v>
+        <v>125.65052</v>
       </c>
       <c r="E42">
-        <f>VLOOKUP(C42,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C42,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>125.65051999999997</v>
       </c>
       <c r="F42" s="3">
         <f t="shared" si="0"/>
-        <v>0.92780925177774221</v>
+        <v>1.0000000000000002</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -2065,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <f>VLOOKUP(C43,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C43,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>119.72</v>
       </c>
       <c r="F43" s="3">
@@ -2087,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <f>VLOOKUP(C44,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C44,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>224.00633999999999</v>
       </c>
       <c r="F44" s="3">
@@ -2109,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <f>VLOOKUP(C45,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C45,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>49.680879999999995</v>
       </c>
       <c r="F45" s="3">
@@ -2131,7 +2137,7 @@
         <v>4.2888860756719822</v>
       </c>
       <c r="E46">
-        <f>VLOOKUP(C46,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C46,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>85.227500000000006</v>
       </c>
       <c r="F46" s="3">
@@ -2153,7 +2159,7 @@
         <v>306.70526266509188</v>
       </c>
       <c r="E47">
-        <f>VLOOKUP(C47,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C47,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>658.37605000000008</v>
       </c>
       <c r="F47" s="3">
@@ -2175,7 +2181,7 @@
         <v>3.1361880225518979</v>
       </c>
       <c r="E48">
-        <f>VLOOKUP(C48,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C48,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>9.7491500000000002</v>
       </c>
       <c r="F48" s="3">
@@ -2197,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <f>VLOOKUP(C49,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C49,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>124.08832</v>
       </c>
       <c r="F49" s="3">
@@ -2219,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <f>VLOOKUP(C50,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C50,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>419.75</v>
       </c>
       <c r="F50" s="3">
@@ -2241,7 +2247,7 @@
         <v>4.0183244254011106</v>
       </c>
       <c r="E51">
-        <f>VLOOKUP(C51,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C51,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>41.0625</v>
       </c>
       <c r="F51" s="3">
@@ -2263,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <f>VLOOKUP(C52,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C52,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>89.972499999999997</v>
       </c>
       <c r="F52" s="3">
@@ -2285,7 +2291,7 @@
         <v>55.881500000000003</v>
       </c>
       <c r="E53">
-        <f>VLOOKUP(C53,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C53,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>55.881500000000003</v>
       </c>
       <c r="F53" s="3">
@@ -2304,15 +2310,15 @@
         <v>56</v>
       </c>
       <c r="D54">
-        <v>18.803363958716929</v>
+        <v>9.732558905401131</v>
       </c>
       <c r="E54">
-        <f>VLOOKUP(C54,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C54,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>70.627499999999998</v>
       </c>
       <c r="F54" s="3">
         <f t="shared" si="0"/>
-        <v>0.26623289736599665</v>
+        <v>0.13780126587237451</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
@@ -2329,7 +2335,7 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <f>VLOOKUP(C55,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C55,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>157.46100000000001</v>
       </c>
       <c r="F55" s="3">
@@ -2351,7 +2357,7 @@
         <v>10.4025</v>
       </c>
       <c r="E56">
-        <f>VLOOKUP(C56,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C56,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10.4025</v>
       </c>
       <c r="F56" s="3">
@@ -2373,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <f>VLOOKUP(C57,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C57,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>63.07200000000001</v>
       </c>
       <c r="F57" s="3">
@@ -2395,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <f>VLOOKUP(C58,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C58,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>233.74600000000001</v>
       </c>
       <c r="F58" s="3">
@@ -2417,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <f>VLOOKUP(C59,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C59,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>36.5</v>
       </c>
       <c r="F59" s="3">
@@ -2439,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <f>VLOOKUP(C60,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C60,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>7.8475000000000001</v>
       </c>
       <c r="F60" s="3">
@@ -2461,7 +2467,7 @@
         <v>3.974396675092017</v>
       </c>
       <c r="E61">
-        <f>VLOOKUP(C61,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C61,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>19.6005</v>
       </c>
       <c r="F61" s="3">
@@ -2483,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <f>VLOOKUP(C62,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C62,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>2.8105000000000002</v>
       </c>
       <c r="F62" s="3">
@@ -2505,7 +2511,7 @@
         <v>17.72805</v>
       </c>
       <c r="E63">
-        <f>VLOOKUP(C63,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C63,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>17.72805</v>
       </c>
       <c r="F63" s="3">
@@ -2527,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <f>VLOOKUP(C64,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C64,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>98.55</v>
       </c>
       <c r="F64" s="3">
@@ -2549,7 +2555,7 @@
         <v>31.263999999999999</v>
       </c>
       <c r="E65">
-        <f>VLOOKUP(C65,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C65,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>81.394999999999996</v>
       </c>
       <c r="F65" s="3">
@@ -2571,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <f>VLOOKUP(C66,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C66,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>60.068779999999997</v>
       </c>
       <c r="F66" s="3">
@@ -2593,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <f>VLOOKUP(C67,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C67,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>1.5034349999999999</v>
       </c>
       <c r="F67" s="3">
@@ -2615,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <f>VLOOKUP(C68,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C68,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>340.03399999999999</v>
       </c>
       <c r="F68" s="3">
@@ -2637,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <f>VLOOKUP(C69,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C69,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>449.59203500000001</v>
       </c>
       <c r="F69" s="3">
@@ -2659,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <f>VLOOKUP(C70,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C70,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10.220000000000001</v>
       </c>
       <c r="F70" s="3">
@@ -2681,7 +2687,7 @@
         <v>225.57591541509191</v>
       </c>
       <c r="E71">
-        <f>VLOOKUP(C71,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C71,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>454.93600000000004</v>
       </c>
       <c r="F71" s="3">
@@ -2703,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <f>VLOOKUP(C72,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C72,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>573.19600000000003</v>
       </c>
       <c r="F72" s="3">
@@ -2725,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <f>VLOOKUP(C73,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C73,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>167.024</v>
       </c>
       <c r="F73" s="3">
@@ -2747,7 +2753,7 @@
         <v>47.048499999999997</v>
       </c>
       <c r="E74">
-        <f>VLOOKUP(C74,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C74,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>47.048499999999997</v>
       </c>
       <c r="F74" s="3">
@@ -2769,7 +2775,7 @@
         <v>151.84</v>
       </c>
       <c r="E75">
-        <f>VLOOKUP(C75,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C75,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>151.84</v>
       </c>
       <c r="F75" s="3">
@@ -2791,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <f>VLOOKUP(C76,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C76,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>28.251000000000005</v>
       </c>
       <c r="F76" s="3">
@@ -2813,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <f>VLOOKUP(C77,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C77,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>18.572295</v>
       </c>
       <c r="F77" s="3">
@@ -2832,15 +2838,15 @@
         <v>80</v>
       </c>
       <c r="D78">
-        <v>35.700498008002278</v>
+        <v>37.466500000000018</v>
       </c>
       <c r="E78">
-        <f>VLOOKUP(C78,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C78,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>51.83</v>
       </c>
       <c r="F78" s="3">
         <f t="shared" si="1"/>
-        <v>0.68879988439132311</v>
+        <v>0.72287285355971487</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
@@ -2854,15 +2860,15 @@
         <v>81</v>
       </c>
       <c r="D79">
-        <v>1.766001991997733</v>
+        <v>0</v>
       </c>
       <c r="E79">
-        <f>VLOOKUP(C79,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C79,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>28.287500000000001</v>
       </c>
       <c r="F79" s="3">
         <f t="shared" si="1"/>
-        <v>6.2430472540794799E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
@@ -2876,15 +2882,15 @@
         <v>82</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1.766001991997733</v>
       </c>
       <c r="E80">
-        <f>VLOOKUP(C80,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C80,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>122.3699</v>
       </c>
       <c r="F80" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.4431669814208665E-2</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
@@ -2901,7 +2907,7 @@
         <v>5</v>
       </c>
       <c r="E81">
-        <f>VLOOKUP(C81,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C81,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>6.5626999999999995</v>
       </c>
       <c r="F81" s="3">
@@ -2923,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <f>VLOOKUP(C82,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C82,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>170.63749999999999</v>
       </c>
       <c r="F82" s="3">
@@ -2945,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <f>VLOOKUP(C83,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C83,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>42.997</v>
       </c>
       <c r="F83" s="3">
@@ -2967,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <f>VLOOKUP(C84,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C84,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>54.074750000000002</v>
       </c>
       <c r="F84" s="3">
@@ -2989,7 +2995,7 @@
         <v>10.40036286731274</v>
       </c>
       <c r="E85">
-        <f>VLOOKUP(C85,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C85,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>12.1837</v>
       </c>
       <c r="F85" s="3">
@@ -3011,7 +3017,7 @@
         <v>23.081527299999991</v>
       </c>
       <c r="E86">
-        <f>VLOOKUP(C86,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C86,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>181.46340000000004</v>
       </c>
       <c r="F86" s="3">
@@ -3033,7 +3039,7 @@
         <v>17.649309599999992</v>
       </c>
       <c r="E87">
-        <f>VLOOKUP(C87,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C87,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>23.659299999999998</v>
       </c>
       <c r="F87" s="3">
@@ -3055,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <f>VLOOKUP(C88,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C88,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>18.359500000000001</v>
       </c>
       <c r="F88" s="3">
@@ -3074,15 +3080,15 @@
         <v>91</v>
       </c>
       <c r="D89">
-        <v>50.12222460951449</v>
+        <v>48.356222617516757</v>
       </c>
       <c r="E89">
-        <f>VLOOKUP(C89,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C89,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>294.09875000000005</v>
       </c>
       <c r="F89" s="3">
         <f t="shared" si="1"/>
-        <v>0.17042651357584648</v>
+        <v>0.16442172099513089</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
@@ -3099,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <f>VLOOKUP(C90,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C90,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>44.603000000000002</v>
       </c>
       <c r="F90" s="3">
@@ -3121,7 +3127,7 @@
         <v>12.91842981977535</v>
       </c>
       <c r="E91">
-        <f>VLOOKUP(C91,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C91,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>20.330500000000001</v>
       </c>
       <c r="F91" s="3">
@@ -3143,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <f>VLOOKUP(C92,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C92,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>24.673999999999996</v>
       </c>
       <c r="F92" s="3">
@@ -3162,15 +3168,15 @@
         <v>95</v>
       </c>
       <c r="D93">
-        <v>22.23007359944231</v>
+        <v>25.084116029688129</v>
       </c>
       <c r="E93">
-        <f>VLOOKUP(C93,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C93,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>41.683</v>
       </c>
       <c r="F93" s="3">
         <f t="shared" si="1"/>
-        <v>0.53331270780515583</v>
+        <v>0.60178288582127315</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
@@ -3187,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <f>VLOOKUP(C94,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C94,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>23.761499999999998</v>
       </c>
       <c r="F94" s="3">
@@ -3206,15 +3212,15 @@
         <v>97</v>
       </c>
       <c r="D95">
-        <v>5.0991688378497741</v>
+        <v>2.2451264076039759</v>
       </c>
       <c r="E95">
-        <f>VLOOKUP(C95,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C95,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>31.024999999999999</v>
       </c>
       <c r="F95" s="3">
         <f t="shared" si="1"/>
-        <v>0.16435677156647138</v>
+        <v>7.2365073573053218E-2</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
@@ -3231,7 +3237,7 @@
         <v>81.906000000000006</v>
       </c>
       <c r="E96">
-        <f>VLOOKUP(C96,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C96,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>81.906000000000006</v>
       </c>
       <c r="F96" s="3">
@@ -3253,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <f>VLOOKUP(C97,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C97,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>52.56</v>
       </c>
       <c r="F97" s="3">
@@ -3275,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="E98">
-        <f>VLOOKUP(C98,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C98,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>29.2</v>
       </c>
       <c r="F98" s="3">
@@ -3297,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <f>VLOOKUP(C99,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C99,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>49.494</v>
       </c>
       <c r="F99" s="3">
@@ -3319,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <f>VLOOKUP(C100,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C100,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>816.06700000000012</v>
       </c>
       <c r="F100" s="3">
@@ -3341,7 +3347,7 @@
         <v>0</v>
       </c>
       <c r="E101">
-        <f>VLOOKUP(C101,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C101,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>188.88749999999999</v>
       </c>
       <c r="F101" s="3">
@@ -3360,15 +3366,15 @@
         <v>104</v>
       </c>
       <c r="D102">
-        <v>83.579562437292097</v>
+        <v>83.579562437292125</v>
       </c>
       <c r="E102">
-        <f>VLOOKUP(C102,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C102,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>424.64100000000008</v>
       </c>
       <c r="F102" s="3">
         <f t="shared" si="1"/>
-        <v>0.19682405240495401</v>
+        <v>0.1968240524049541</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
@@ -3385,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <f>VLOOKUP(C103,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C103,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>0.80300000000000016</v>
       </c>
       <c r="F103" s="3">
@@ -3407,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <f>VLOOKUP(C104,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C104,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>635.83000000000004</v>
       </c>
       <c r="F104" s="3">
@@ -3429,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="E105">
-        <f>VLOOKUP(C105,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C105,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>61.32</v>
       </c>
       <c r="F105" s="3">
@@ -3451,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <f>VLOOKUP(C106,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C106,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>80.3</v>
       </c>
       <c r="F106" s="3">
@@ -3473,7 +3479,7 @@
         <v>0.55586415</v>
       </c>
       <c r="E107">
-        <f>VLOOKUP(C107,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C107,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>200.71350000000001</v>
       </c>
       <c r="F107" s="3">
@@ -3495,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <f>VLOOKUP(C108,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C108,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>256.15699999999998</v>
       </c>
       <c r="F108" s="3">
@@ -3517,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <f>VLOOKUP(C109,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C109,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>145.489</v>
       </c>
       <c r="F109" s="3">
@@ -3539,7 +3545,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <f>VLOOKUP(C110,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C110,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>161.62200000000001</v>
       </c>
       <c r="F110" s="3">
@@ -3558,15 +3564,15 @@
         <v>113</v>
       </c>
       <c r="D111">
-        <v>365.89085980871693</v>
+        <v>356.82005475540097</v>
       </c>
       <c r="E111">
-        <f>VLOOKUP(C111,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C111,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>421.21</v>
       </c>
       <c r="F111" s="3">
         <f t="shared" si="1"/>
-        <v>0.86866612808033272</v>
+        <v>0.8471310148272857</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
@@ -3583,7 +3589,7 @@
         <v>129.941</v>
       </c>
       <c r="E112">
-        <f>VLOOKUP(C112,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C112,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>180.20050000000001</v>
       </c>
       <c r="F112" s="3">
@@ -3605,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="E113">
-        <f>VLOOKUP(C113,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C113,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>439.27749999999992</v>
       </c>
       <c r="F113" s="3">
@@ -3627,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="E114">
-        <f>VLOOKUP(C114,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C114,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>118.77099999999999</v>
       </c>
       <c r="F114" s="3">
@@ -3646,15 +3652,15 @@
         <v>117</v>
       </c>
       <c r="D115">
-        <v>27.329242437292081</v>
+        <v>27.329242437292109</v>
       </c>
       <c r="E115">
-        <f>VLOOKUP(C115,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C115,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>486.91</v>
       </c>
       <c r="F115" s="3">
         <f t="shared" si="1"/>
-        <v>5.612791365404711E-2</v>
+        <v>5.6127913654047172E-2</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.35">
@@ -3671,7 +3677,7 @@
         <v>0</v>
       </c>
       <c r="E116">
-        <f>VLOOKUP(C116,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C116,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>144.17500000000001</v>
       </c>
       <c r="F116" s="3">
@@ -3693,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="E117">
-        <f>VLOOKUP(C117,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C117,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>61.32</v>
       </c>
       <c r="F117" s="3">
@@ -3715,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="E118">
-        <f>VLOOKUP(C118,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C118,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>123.04150000000001</v>
       </c>
       <c r="F118" s="3">
@@ -3737,7 +3743,7 @@
         <v>455.15499999999997</v>
       </c>
       <c r="E119">
-        <f>VLOOKUP(C119,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C119,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>455.15499999999997</v>
       </c>
       <c r="F119" s="3">
@@ -3759,7 +3765,7 @@
         <v>351.714</v>
       </c>
       <c r="E120">
-        <f>VLOOKUP(C120,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C120,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>351.714</v>
       </c>
       <c r="F120" s="3">
@@ -3781,7 +3787,7 @@
         <v>143.5657628199998</v>
       </c>
       <c r="E121">
-        <f>VLOOKUP(C121,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C121,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>167.75399999999999</v>
       </c>
       <c r="F121" s="3">
@@ -3803,7 +3809,7 @@
         <v>24.41750027000003</v>
       </c>
       <c r="E122">
-        <f>VLOOKUP(C122,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C122,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>207.5025</v>
       </c>
       <c r="F122" s="3">
@@ -3825,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="E123">
-        <f>VLOOKUP(C123,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C123,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>513.19000000000005</v>
       </c>
       <c r="F123" s="3">
@@ -3844,15 +3850,15 @@
         <v>125</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>37.970449233315946</v>
       </c>
       <c r="E124">
-        <f>VLOOKUP(C124,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C124,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>67.451999999999998</v>
       </c>
       <c r="F124" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.56292547638788992</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -3869,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="E125">
-        <f>VLOOKUP(C125,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C125,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>200.71350000000001</v>
       </c>
       <c r="F125" s="3">
@@ -3891,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="E126">
-        <f>VLOOKUP(C126,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C126,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>123.04150000000001</v>
       </c>
       <c r="F126" s="3">
@@ -3910,15 +3916,15 @@
         <v>128</v>
       </c>
       <c r="D127">
-        <v>347.32785980871688</v>
+        <v>338.25705475540099</v>
       </c>
       <c r="E127">
-        <f>VLOOKUP(C127,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C127,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>421.21</v>
       </c>
       <c r="F127" s="3">
         <f t="shared" si="1"/>
-        <v>0.82459547448711312</v>
+        <v>0.8030603612340661</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -3935,7 +3941,7 @@
         <v>10.747</v>
       </c>
       <c r="E128">
-        <f>VLOOKUP(C128,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C128,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>14.965</v>
       </c>
       <c r="F128" s="3">
@@ -3957,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <f>VLOOKUP(C129,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C129,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>439.27749999999992</v>
       </c>
       <c r="F129" s="3">
@@ -3979,7 +3985,7 @@
         <v>117.4935</v>
       </c>
       <c r="E130">
-        <f>VLOOKUP(C130,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C130,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>117.49349999999998</v>
       </c>
       <c r="F130" s="3">
@@ -4001,11 +4007,11 @@
         <v>91.526676324328051</v>
       </c>
       <c r="E131">
-        <f>VLOOKUP(C131,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C131,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>117.49349999999998</v>
       </c>
       <c r="F131" s="3">
-        <f t="shared" ref="F131:F147" si="2">D131/E131</f>
+        <f t="shared" ref="F131:F149" si="2">D131/E131</f>
         <v>0.77899353006190186</v>
       </c>
     </row>
@@ -4017,18 +4023,18 @@
         <v>3</v>
       </c>
       <c r="C132" t="s">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="D132">
-        <v>0.55586415</v>
+        <v>0</v>
       </c>
       <c r="E132">
-        <f>VLOOKUP(C132,Sheet2!$C$1:$D$147,2,FALSE)</f>
-        <v>10000</v>
+        <f>VLOOKUP(C132,Sheet2!$C$1:$D$149,2,FALSE)</f>
+        <v>24.424999999999997</v>
       </c>
       <c r="F132" s="3">
         <f t="shared" si="2"/>
-        <v>5.5586415000000001E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.35">
@@ -4039,18 +4045,18 @@
         <v>3</v>
       </c>
       <c r="C133" t="s">
-        <v>134</v>
+        <v>241</v>
       </c>
       <c r="D133">
-        <v>347.32785980871688</v>
+        <v>0</v>
       </c>
       <c r="E133">
-        <f>VLOOKUP(C133,Sheet2!$C$1:$D$147,2,FALSE)</f>
-        <v>10000</v>
+        <f>VLOOKUP(C133,Sheet2!$C$1:$D$149,2,FALSE)</f>
+        <v>24.424999999999997</v>
       </c>
       <c r="F133" s="3">
         <f t="shared" si="2"/>
-        <v>3.4732785980871685E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
@@ -4061,18 +4067,18 @@
         <v>3</v>
       </c>
       <c r="C134" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D134">
-        <v>7.5617455199999997</v>
+        <v>0.55586415</v>
       </c>
       <c r="E134">
-        <f>VLOOKUP(C134,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C134,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F134" s="3">
         <f t="shared" si="2"/>
-        <v>7.5617455199999994E-4</v>
+        <v>5.5586415000000001E-5</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.35">
@@ -4083,18 +4089,18 @@
         <v>3</v>
       </c>
       <c r="C135" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D135">
-        <v>5.7643000000000007E-2</v>
+        <v>338.25705475540099</v>
       </c>
       <c r="E135">
-        <f>VLOOKUP(C135,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C135,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F135" s="3">
         <f t="shared" si="2"/>
-        <v>5.7643000000000009E-6</v>
+        <v>3.3825705475540098E-2</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
@@ -4105,18 +4111,18 @@
         <v>3</v>
       </c>
       <c r="C136" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D136">
-        <v>0.53100926999999998</v>
+        <v>7.5617455199999997</v>
       </c>
       <c r="E136">
-        <f>VLOOKUP(C136,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C136,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F136" s="3">
         <f t="shared" si="2"/>
-        <v>5.3100926999999999E-5</v>
+        <v>7.5617455199999994E-4</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
@@ -4127,18 +4133,18 @@
         <v>3</v>
       </c>
       <c r="C137" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D137">
-        <v>8.6795214499999993</v>
+        <v>5.7643000000000007E-2</v>
       </c>
       <c r="E137">
-        <f>VLOOKUP(C137,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C137,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F137" s="3">
         <f t="shared" si="2"/>
-        <v>8.6795214499999992E-4</v>
+        <v>5.7643000000000009E-6</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
@@ -4149,18 +4155,18 @@
         <v>3</v>
       </c>
       <c r="C138" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D138">
-        <v>1.91565275</v>
+        <v>0.53100926999999998</v>
       </c>
       <c r="E138">
-        <f>VLOOKUP(C138,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C138,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F138" s="3">
         <f t="shared" si="2"/>
-        <v>1.91565275E-4</v>
+        <v>5.3100926999999999E-5</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
@@ -4171,18 +4177,18 @@
         <v>3</v>
       </c>
       <c r="C139" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D139">
-        <v>0.16949972999999999</v>
+        <v>8.6795214499999993</v>
       </c>
       <c r="E139">
-        <f>VLOOKUP(C139,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C139,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F139" s="3">
         <f t="shared" si="2"/>
-        <v>1.6949972999999998E-5</v>
+        <v>8.6795214499999992E-4</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
@@ -4193,18 +4199,18 @@
         <v>3</v>
       </c>
       <c r="C140" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D140">
-        <v>6.3309600000000021E-2</v>
+        <v>1.91565275</v>
       </c>
       <c r="E140">
-        <f>VLOOKUP(C140,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C140,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F140" s="3">
         <f t="shared" si="2"/>
-        <v>6.3309600000000023E-6</v>
+        <v>1.91565275E-4</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.35">
@@ -4215,18 +4221,18 @@
         <v>3</v>
       </c>
       <c r="C141" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D141">
-        <v>16.46245</v>
+        <v>0.16949972999999999</v>
       </c>
       <c r="E141">
-        <f>VLOOKUP(C141,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C141,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F141" s="3">
         <f t="shared" si="2"/>
-        <v>1.646245E-3</v>
+        <v>1.6949972999999998E-5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
@@ -4237,18 +4243,18 @@
         <v>3</v>
       </c>
       <c r="C142" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>6.3309600000000021E-2</v>
       </c>
       <c r="E142">
-        <f>VLOOKUP(C142,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C142,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F142" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6.3309600000000023E-6</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.35">
@@ -4259,18 +4265,18 @@
         <v>3</v>
       </c>
       <c r="C143" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D143">
-        <v>3.99593</v>
+        <v>16.46245</v>
       </c>
       <c r="E143">
-        <f>VLOOKUP(C143,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C143,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F143" s="3">
         <f t="shared" si="2"/>
-        <v>3.9959300000000001E-4</v>
+        <v>1.646245E-3</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.35">
@@ -4281,18 +4287,18 @@
         <v>3</v>
       </c>
       <c r="C144" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D144">
-        <v>0.6516687699999999</v>
+        <v>0</v>
       </c>
       <c r="E144">
-        <f>VLOOKUP(C144,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C144,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F144" s="3">
         <f t="shared" si="2"/>
-        <v>6.5166876999999985E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.35">
@@ -4303,18 +4309,18 @@
         <v>3</v>
       </c>
       <c r="C145" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D145">
-        <v>5.2113180000000002E-2</v>
+        <v>3.99593</v>
       </c>
       <c r="E145">
-        <f>VLOOKUP(C145,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C145,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F145" s="3">
         <f t="shared" si="2"/>
-        <v>5.2113180000000005E-6</v>
+        <v>3.9959300000000001E-4</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.35">
@@ -4325,18 +4331,18 @@
         <v>3</v>
       </c>
       <c r="C146" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D146">
-        <v>4.2744726999999996</v>
+        <v>0.6516687699999999</v>
       </c>
       <c r="E146">
-        <f>VLOOKUP(C146,Sheet2!$C$1:$D$147,2,FALSE)</f>
+        <f>VLOOKUP(C146,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
       <c r="F146" s="3">
         <f t="shared" si="2"/>
-        <v>4.2744726999999997E-4</v>
+        <v>6.5166876999999985E-5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
@@ -4347,16 +4353,60 @@
         <v>3</v>
       </c>
       <c r="C147" t="s">
+        <v>146</v>
+      </c>
+      <c r="D147">
+        <v>5.2113180000000002E-2</v>
+      </c>
+      <c r="E147">
+        <f>VLOOKUP(C147,Sheet2!$C$1:$D$149,2,FALSE)</f>
+        <v>10000</v>
+      </c>
+      <c r="F147" s="3">
+        <f t="shared" si="2"/>
+        <v>5.2113180000000005E-6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A148" s="1">
+        <v>146</v>
+      </c>
+      <c r="B148" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" t="s">
+        <v>147</v>
+      </c>
+      <c r="D148">
+        <v>4.2744726999999996</v>
+      </c>
+      <c r="E148">
+        <f>VLOOKUP(C148,Sheet2!$C$1:$D$149,2,FALSE)</f>
+        <v>10000</v>
+      </c>
+      <c r="F148" s="3">
+        <f t="shared" si="2"/>
+        <v>4.2744726999999997E-4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A149" s="1">
+        <v>147</v>
+      </c>
+      <c r="B149" t="s">
+        <v>3</v>
+      </c>
+      <c r="C149" t="s">
         <v>148</v>
       </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-      <c r="E147">
-        <f>VLOOKUP(C147,Sheet2!$C$1:$D$147,2,FALSE)</f>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <f>VLOOKUP(C149,Sheet2!$C$1:$D$149,2,FALSE)</f>
         <v>10000</v>
       </c>
-      <c r="F147" s="3">
+      <c r="F149" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -4368,7 +4418,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F05331-0857-44A4-85ED-5A98C362AF86}">
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M149"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="13.6328125" customWidth="1"/>
@@ -6335,7 +6385,7 @@
         <v>198</v>
       </c>
       <c r="C130" t="str">
-        <f t="shared" ref="C130:C147" si="2">_xlfn.CONCAT("('",A130,"', '",B130,"')")</f>
+        <f t="shared" ref="C130:C149" si="2">_xlfn.CONCAT("('",A130,"', '",B130,"')")</f>
         <v>('RS', 'HU')</v>
       </c>
       <c r="D130">
@@ -6595,6 +6645,36 @@
       </c>
       <c r="D147">
         <v>117.49349999999998</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>174</v>
+      </c>
+      <c r="B148" t="s">
+        <v>182</v>
+      </c>
+      <c r="C148" t="str">
+        <f t="shared" si="2"/>
+        <v>('EE', 'LV')</v>
+      </c>
+      <c r="D148">
+        <v>24.424999999999997</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>182</v>
+      </c>
+      <c r="B149" t="s">
+        <v>174</v>
+      </c>
+      <c r="C149" t="str">
+        <f t="shared" si="2"/>
+        <v>('LV', 'EE')</v>
+      </c>
+      <c r="D149">
+        <v>24.424999999999997</v>
       </c>
     </row>
   </sheetData>
